--- a/Documentation/trials.xlsx
+++ b/Documentation/trials.xlsx
@@ -29,7 +29,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00000000"/>
       <sz val="13"/>
     </font>
     <font>
@@ -522,20 +521,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,120 +555,114 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>outcome and stage_reached have dropdowns. stage_reached applies only to assembly attachments.</t>
+          <t>outcome, failure_cause, and stage_reached have dropdowns. stage_reached applies only to assembly attachments.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Each ball-valve configuration is a separate set of 5 trials (with and without the friction ring).</t>
+          <t>failure_cause is required for fail/timeout/safety_stop rows; leave blank on success.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>Each ball-valve configuration is a separate set of 5 trials (with and without the friction ring).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>See HOW_TO_FILL_TRIALS.md for instructions and PROTOCOL.md for success criteria and timeouts.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>trial_id</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>lab_id</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>platform_id</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>attachment_id</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>outcome</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>failure_cause</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>completion_time_s</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>n_attempts</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>n_regrasps</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>stage_reached</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Torque</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>valve_ball</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="8" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
@@ -684,10 +678,11 @@
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
@@ -703,10 +698,11 @@
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n"/>
       <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
@@ -722,10 +718,11 @@
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -741,16 +738,17 @@
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="8" t="n"/>
       <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>valve_ball_ring</t>
+          <t>valve_ball</t>
         </is>
       </c>
       <c r="E14" s="9" t="n"/>
@@ -760,10 +758,11 @@
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
@@ -779,10 +778,11 @@
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n"/>
       <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
@@ -798,10 +798,11 @@
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
@@ -817,10 +818,11 @@
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="8" t="n"/>
       <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
@@ -836,16 +838,17 @@
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>valve_gate_small</t>
+          <t>valve_ball_ring</t>
         </is>
       </c>
       <c r="E19" s="9" t="n"/>
@@ -855,10 +858,11 @@
       <c r="I19" s="8" t="n"/>
       <c r="J19" s="8" t="n"/>
       <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
@@ -874,10 +878,11 @@
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
@@ -893,10 +898,11 @@
       <c r="I21" s="8" t="n"/>
       <c r="J21" s="8" t="n"/>
       <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
@@ -912,10 +918,11 @@
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
@@ -931,16 +938,17 @@
       <c r="I23" s="8" t="n"/>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>valve_gate_large</t>
+          <t>valve_gate_small</t>
         </is>
       </c>
       <c r="E24" s="9" t="n"/>
@@ -950,10 +958,11 @@
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
@@ -969,10 +978,11 @@
       <c r="I25" s="8" t="n"/>
       <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n"/>
+      <c r="L25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
@@ -988,10 +998,11 @@
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
@@ -1007,10 +1018,11 @@
       <c r="I27" s="8" t="n"/>
       <c r="J27" s="8" t="n"/>
       <c r="K27" s="8" t="n"/>
+      <c r="L27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -1026,16 +1038,17 @@
       <c r="I28" s="8" t="n"/>
       <c r="J28" s="8" t="n"/>
       <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>circuit_breaker</t>
+          <t>valve_gate_large</t>
         </is>
       </c>
       <c r="E29" s="9" t="n"/>
@@ -1045,10 +1058,11 @@
       <c r="I29" s="8" t="n"/>
       <c r="J29" s="8" t="n"/>
       <c r="K29" s="8" t="n"/>
+      <c r="L29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
@@ -1064,10 +1078,11 @@
       <c r="I30" s="8" t="n"/>
       <c r="J30" s="8" t="n"/>
       <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="8" t="n"/>
@@ -1083,10 +1098,11 @@
       <c r="I31" s="8" t="n"/>
       <c r="J31" s="8" t="n"/>
       <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="8" t="n"/>
@@ -1102,10 +1118,11 @@
       <c r="I32" s="8" t="n"/>
       <c r="J32" s="8" t="n"/>
       <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
@@ -1121,46 +1138,49 @@
       <c r="I33" s="8" t="n"/>
       <c r="J33" s="8" t="n"/>
       <c r="K33" s="8" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="L33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>circuit_breaker</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Precision</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="11" t="n"/>
-      <c r="I34" s="11" t="n"/>
-      <c r="J34" s="11" t="n"/>
-      <c r="K34" s="11" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>light_bulb</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="11" t="n"/>
+      <c r="L35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B36" s="13" t="n"/>
       <c r="C36" s="13" t="n"/>
@@ -1176,10 +1196,11 @@
       <c r="I36" s="13" t="n"/>
       <c r="J36" s="13" t="n"/>
       <c r="K36" s="13" t="n"/>
+      <c r="L36" s="13" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" s="13" t="n"/>
       <c r="C37" s="13" t="n"/>
@@ -1195,10 +1216,11 @@
       <c r="I37" s="13" t="n"/>
       <c r="J37" s="13" t="n"/>
       <c r="K37" s="13" t="n"/>
+      <c r="L37" s="13" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38" s="13" t="n"/>
       <c r="C38" s="13" t="n"/>
@@ -1214,10 +1236,11 @@
       <c r="I38" s="13" t="n"/>
       <c r="J38" s="13" t="n"/>
       <c r="K38" s="13" t="n"/>
+      <c r="L38" s="13" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39" s="13" t="n"/>
       <c r="C39" s="13" t="n"/>
@@ -1233,16 +1256,17 @@
       <c r="I39" s="13" t="n"/>
       <c r="J39" s="13" t="n"/>
       <c r="K39" s="13" t="n"/>
+      <c r="L39" s="13" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40" s="13" t="n"/>
       <c r="C40" s="13" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>thread_m8</t>
+          <t>light_bulb</t>
         </is>
       </c>
       <c r="E40" s="14" t="n"/>
@@ -1252,10 +1276,11 @@
       <c r="I40" s="13" t="n"/>
       <c r="J40" s="13" t="n"/>
       <c r="K40" s="13" t="n"/>
+      <c r="L40" s="13" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B41" s="13" t="n"/>
       <c r="C41" s="13" t="n"/>
@@ -1271,10 +1296,11 @@
       <c r="I41" s="13" t="n"/>
       <c r="J41" s="13" t="n"/>
       <c r="K41" s="13" t="n"/>
+      <c r="L41" s="13" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B42" s="13" t="n"/>
       <c r="C42" s="13" t="n"/>
@@ -1290,10 +1316,11 @@
       <c r="I42" s="13" t="n"/>
       <c r="J42" s="13" t="n"/>
       <c r="K42" s="13" t="n"/>
+      <c r="L42" s="13" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" s="13" t="n"/>
       <c r="C43" s="13" t="n"/>
@@ -1309,10 +1336,11 @@
       <c r="I43" s="13" t="n"/>
       <c r="J43" s="13" t="n"/>
       <c r="K43" s="13" t="n"/>
+      <c r="L43" s="13" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B44" s="13" t="n"/>
       <c r="C44" s="13" t="n"/>
@@ -1328,16 +1356,17 @@
       <c r="I44" s="13" t="n"/>
       <c r="J44" s="13" t="n"/>
       <c r="K44" s="13" t="n"/>
+      <c r="L44" s="13" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B45" s="13" t="n"/>
       <c r="C45" s="13" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>thread_m30</t>
+          <t>thread_m8</t>
         </is>
       </c>
       <c r="E45" s="14" t="n"/>
@@ -1347,10 +1376,11 @@
       <c r="I45" s="13" t="n"/>
       <c r="J45" s="13" t="n"/>
       <c r="K45" s="13" t="n"/>
+      <c r="L45" s="13" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B46" s="13" t="n"/>
       <c r="C46" s="13" t="n"/>
@@ -1366,10 +1396,11 @@
       <c r="I46" s="13" t="n"/>
       <c r="J46" s="13" t="n"/>
       <c r="K46" s="13" t="n"/>
+      <c r="L46" s="13" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B47" s="13" t="n"/>
       <c r="C47" s="13" t="n"/>
@@ -1385,10 +1416,11 @@
       <c r="I47" s="13" t="n"/>
       <c r="J47" s="13" t="n"/>
       <c r="K47" s="13" t="n"/>
+      <c r="L47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" s="13" t="n"/>
       <c r="C48" s="13" t="n"/>
@@ -1404,10 +1436,11 @@
       <c r="I48" s="13" t="n"/>
       <c r="J48" s="13" t="n"/>
       <c r="K48" s="13" t="n"/>
+      <c r="L48" s="13" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="13" t="n"/>
       <c r="C49" s="13" t="n"/>
@@ -1423,16 +1456,17 @@
       <c r="I49" s="13" t="n"/>
       <c r="J49" s="13" t="n"/>
       <c r="K49" s="13" t="n"/>
+      <c r="L49" s="13" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" s="13" t="n"/>
       <c r="C50" s="13" t="n"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>peg_insertion</t>
+          <t>thread_m30</t>
         </is>
       </c>
       <c r="E50" s="14" t="n"/>
@@ -1442,10 +1476,11 @@
       <c r="I50" s="13" t="n"/>
       <c r="J50" s="13" t="n"/>
       <c r="K50" s="13" t="n"/>
+      <c r="L50" s="13" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B51" s="13" t="n"/>
       <c r="C51" s="13" t="n"/>
@@ -1461,10 +1496,11 @@
       <c r="I51" s="13" t="n"/>
       <c r="J51" s="13" t="n"/>
       <c r="K51" s="13" t="n"/>
+      <c r="L51" s="13" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B52" s="13" t="n"/>
       <c r="C52" s="13" t="n"/>
@@ -1480,10 +1516,11 @@
       <c r="I52" s="13" t="n"/>
       <c r="J52" s="13" t="n"/>
       <c r="K52" s="13" t="n"/>
+      <c r="L52" s="13" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B53" s="13" t="n"/>
       <c r="C53" s="13" t="n"/>
@@ -1499,10 +1536,11 @@
       <c r="I53" s="13" t="n"/>
       <c r="J53" s="13" t="n"/>
       <c r="K53" s="13" t="n"/>
+      <c r="L53" s="13" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B54" s="13" t="n"/>
       <c r="C54" s="13" t="n"/>
@@ -1518,46 +1556,49 @@
       <c r="I54" s="13" t="n"/>
       <c r="J54" s="13" t="n"/>
       <c r="K54" s="13" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="L54" s="13" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="13" t="n"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>peg_insertion</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="n"/>
+      <c r="F55" s="13" t="n"/>
+      <c r="G55" s="13" t="n"/>
+      <c r="H55" s="13" t="n"/>
+      <c r="I55" s="13" t="n"/>
+      <c r="J55" s="13" t="n"/>
+      <c r="K55" s="13" t="n"/>
+      <c r="L55" s="13" t="n"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Assembly</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n"/>
-      <c r="C55" s="16" t="n"/>
-      <c r="D55" s="16" t="n"/>
-      <c r="E55" s="17" t="n"/>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="16" t="n"/>
-      <c r="H55" s="16" t="n"/>
-      <c r="I55" s="16" t="n"/>
-      <c r="J55" s="16" t="n"/>
-      <c r="K55" s="16" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B56" s="18" t="n"/>
-      <c r="C56" s="18" t="n"/>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>button</t>
-        </is>
-      </c>
-      <c r="E56" s="19" t="n"/>
-      <c r="F56" s="18" t="n"/>
-      <c r="G56" s="18" t="n"/>
-      <c r="H56" s="18" t="n"/>
-      <c r="I56" s="18" t="n"/>
-      <c r="J56" s="18" t="n"/>
-      <c r="K56" s="18" t="n"/>
+      <c r="B56" s="16" t="n"/>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="16" t="n"/>
+      <c r="I56" s="16" t="n"/>
+      <c r="J56" s="16" t="n"/>
+      <c r="K56" s="16" t="n"/>
+      <c r="L56" s="16" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" s="18" t="n"/>
       <c r="C57" s="18" t="n"/>
@@ -1573,10 +1614,11 @@
       <c r="I57" s="18" t="n"/>
       <c r="J57" s="18" t="n"/>
       <c r="K57" s="18" t="n"/>
+      <c r="L57" s="18" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B58" s="18" t="n"/>
       <c r="C58" s="18" t="n"/>
@@ -1592,10 +1634,11 @@
       <c r="I58" s="18" t="n"/>
       <c r="J58" s="18" t="n"/>
       <c r="K58" s="18" t="n"/>
+      <c r="L58" s="18" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B59" s="18" t="n"/>
       <c r="C59" s="18" t="n"/>
@@ -1611,10 +1654,11 @@
       <c r="I59" s="18" t="n"/>
       <c r="J59" s="18" t="n"/>
       <c r="K59" s="18" t="n"/>
+      <c r="L59" s="18" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B60" s="18" t="n"/>
       <c r="C60" s="18" t="n"/>
@@ -1630,16 +1674,17 @@
       <c r="I60" s="18" t="n"/>
       <c r="J60" s="18" t="n"/>
       <c r="K60" s="18" t="n"/>
+      <c r="L60" s="18" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B61" s="18" t="n"/>
       <c r="C61" s="18" t="n"/>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>lock</t>
+          <t>button</t>
         </is>
       </c>
       <c r="E61" s="19" t="n"/>
@@ -1649,10 +1694,11 @@
       <c r="I61" s="18" t="n"/>
       <c r="J61" s="18" t="n"/>
       <c r="K61" s="18" t="n"/>
+      <c r="L61" s="18" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B62" s="18" t="n"/>
       <c r="C62" s="18" t="n"/>
@@ -1668,10 +1714,11 @@
       <c r="I62" s="18" t="n"/>
       <c r="J62" s="18" t="n"/>
       <c r="K62" s="18" t="n"/>
+      <c r="L62" s="18" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B63" s="18" t="n"/>
       <c r="C63" s="18" t="n"/>
@@ -1687,10 +1734,11 @@
       <c r="I63" s="18" t="n"/>
       <c r="J63" s="18" t="n"/>
       <c r="K63" s="18" t="n"/>
+      <c r="L63" s="18" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B64" s="18" t="n"/>
       <c r="C64" s="18" t="n"/>
@@ -1706,10 +1754,11 @@
       <c r="I64" s="18" t="n"/>
       <c r="J64" s="18" t="n"/>
       <c r="K64" s="18" t="n"/>
+      <c r="L64" s="18" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B65" s="18" t="n"/>
       <c r="C65" s="18" t="n"/>
@@ -1725,16 +1774,17 @@
       <c r="I65" s="18" t="n"/>
       <c r="J65" s="18" t="n"/>
       <c r="K65" s="18" t="n"/>
+      <c r="L65" s="18" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B66" s="18" t="n"/>
       <c r="C66" s="18" t="n"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>drawer</t>
+          <t>lock</t>
         </is>
       </c>
       <c r="E66" s="19" t="n"/>
@@ -1744,10 +1794,11 @@
       <c r="I66" s="18" t="n"/>
       <c r="J66" s="18" t="n"/>
       <c r="K66" s="18" t="n"/>
+      <c r="L66" s="18" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B67" s="18" t="n"/>
       <c r="C67" s="18" t="n"/>
@@ -1763,10 +1814,11 @@
       <c r="I67" s="18" t="n"/>
       <c r="J67" s="18" t="n"/>
       <c r="K67" s="18" t="n"/>
+      <c r="L67" s="18" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B68" s="18" t="n"/>
       <c r="C68" s="18" t="n"/>
@@ -1782,10 +1834,11 @@
       <c r="I68" s="18" t="n"/>
       <c r="J68" s="18" t="n"/>
       <c r="K68" s="18" t="n"/>
+      <c r="L68" s="18" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B69" s="18" t="n"/>
       <c r="C69" s="18" t="n"/>
@@ -1801,10 +1854,11 @@
       <c r="I69" s="18" t="n"/>
       <c r="J69" s="18" t="n"/>
       <c r="K69" s="18" t="n"/>
+      <c r="L69" s="18" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B70" s="18" t="n"/>
       <c r="C70" s="18" t="n"/>
@@ -1820,16 +1874,17 @@
       <c r="I70" s="18" t="n"/>
       <c r="J70" s="18" t="n"/>
       <c r="K70" s="18" t="n"/>
+      <c r="L70" s="18" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B71" s="18" t="n"/>
       <c r="C71" s="18" t="n"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>shock_absorber</t>
+          <t>drawer</t>
         </is>
       </c>
       <c r="E71" s="19" t="n"/>
@@ -1839,10 +1894,11 @@
       <c r="I71" s="18" t="n"/>
       <c r="J71" s="18" t="n"/>
       <c r="K71" s="18" t="n"/>
+      <c r="L71" s="18" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B72" s="18" t="n"/>
       <c r="C72" s="18" t="n"/>
@@ -1858,10 +1914,11 @@
       <c r="I72" s="18" t="n"/>
       <c r="J72" s="18" t="n"/>
       <c r="K72" s="18" t="n"/>
+      <c r="L72" s="18" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B73" s="18" t="n"/>
       <c r="C73" s="18" t="n"/>
@@ -1877,10 +1934,11 @@
       <c r="I73" s="18" t="n"/>
       <c r="J73" s="18" t="n"/>
       <c r="K73" s="18" t="n"/>
+      <c r="L73" s="18" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B74" s="18" t="n"/>
       <c r="C74" s="18" t="n"/>
@@ -1896,10 +1954,11 @@
       <c r="I74" s="18" t="n"/>
       <c r="J74" s="18" t="n"/>
       <c r="K74" s="18" t="n"/>
+      <c r="L74" s="18" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B75" s="18" t="n"/>
       <c r="C75" s="18" t="n"/>
@@ -1915,32 +1974,57 @@
       <c r="I75" s="18" t="n"/>
       <c r="J75" s="18" t="n"/>
       <c r="K75" s="18" t="n"/>
+      <c r="L75" s="18" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B76" s="18" t="n"/>
+      <c r="C76" s="18" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>shock_absorber</t>
+        </is>
+      </c>
+      <c r="E76" s="19" t="n"/>
+      <c r="F76" s="18" t="n"/>
+      <c r="G76" s="18" t="n"/>
+      <c r="H76" s="18" t="n"/>
+      <c r="I76" s="18" t="n"/>
+      <c r="J76" s="18" t="n"/>
+      <c r="K76" s="18" t="n"/>
+      <c r="L76" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A8:K8"/>
+  <mergeCells count="9">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation sqref="F8:F75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid outcome" error="Pick one of: success, fail, timeout, safety_stop" type="list">
+  <dataValidations count="6">
+    <dataValidation sqref="F9:F76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"success,fail,timeout,safety_stop"</formula1>
     </dataValidation>
-    <dataValidation sqref="J8:J75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid stage" error="Stage must be 1, 2, or 3 (only for assembly attachments)" type="list">
+    <dataValidation sqref="G9:G76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"grasp_geometry,kinematic_limit,perception,slip,control_precision,other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K9:K76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
-    <dataValidation sqref="H8:H75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="n_attempts must be a non-negative integer" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="I9:I76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="I8:I75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="n_regrasps must be a non-negative integer" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="J9:J76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="G8:G75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid time" error="completion_time_s must be non-negative; blank for non-success rows" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="H9:H76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0.0</formula1>
     </dataValidation>
   </dataValidations>

--- a/Documentation/trials.xlsx
+++ b/Documentation/trials.xlsx
@@ -526,7 +526,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -535,7 +535,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2013,7 +2013,7 @@
       <formula1>"success,fail,timeout,safety_stop"</formula1>
     </dataValidation>
     <dataValidation sqref="G9:G76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"grasp_geometry,kinematic_limit,perception,slip,control_precision,other"</formula1>
+      <formula1>"grasp_geometry,kinematic_limit,perception,slip,force_limit,control_precision,other"</formula1>
     </dataValidation>
     <dataValidation sqref="K9:K76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3"</formula1>

--- a/Documentation/trials.xlsx
+++ b/Documentation/trials.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,8 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,7 +556,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>outcome, failure_cause, and stage_reached have dropdowns. stage_reached applies only to assembly attachments.</t>
+          <t>outcome, failure_cause, stage_reached, and strategy have dropdowns. stage_reached applies only to assembly attachments.</t>
         </is>
       </c>
     </row>
@@ -580,6 +581,13 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>completion_time_s is decimal seconds. n_attempts counts from 1, n_regrasps from 0. Fill n_attempts, n_regrasps, and strategy on failed rows too.</t>
+        </is>
+      </c>
+    </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -638,6 +646,11 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -648,17 +661,6 @@
           <t xml:space="preserve">  Torque</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -678,7 +680,7 @@
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -698,7 +700,7 @@
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n"/>
       <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -718,7 +720,7 @@
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -738,7 +740,7 @@
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="8" t="n"/>
       <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -758,7 +760,7 @@
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -778,7 +780,7 @@
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n"/>
       <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -798,7 +800,7 @@
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -818,7 +820,7 @@
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="8" t="n"/>
       <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -838,7 +840,7 @@
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -858,7 +860,7 @@
       <c r="I19" s="8" t="n"/>
       <c r="J19" s="8" t="n"/>
       <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -878,7 +880,7 @@
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -898,7 +900,7 @@
       <c r="I21" s="8" t="n"/>
       <c r="J21" s="8" t="n"/>
       <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -918,7 +920,7 @@
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -938,7 +940,7 @@
       <c r="I23" s="8" t="n"/>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -958,7 +960,7 @@
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -978,7 +980,7 @@
       <c r="I25" s="8" t="n"/>
       <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n"/>
-      <c r="L25" s="8" t="n"/>
+      <c r="M25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -998,7 +1000,7 @@
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
-      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1018,7 +1020,7 @@
       <c r="I27" s="8" t="n"/>
       <c r="J27" s="8" t="n"/>
       <c r="K27" s="8" t="n"/>
-      <c r="L27" s="8" t="n"/>
+      <c r="M27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -1038,7 +1040,7 @@
       <c r="I28" s="8" t="n"/>
       <c r="J28" s="8" t="n"/>
       <c r="K28" s="8" t="n"/>
-      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -1058,7 +1060,7 @@
       <c r="I29" s="8" t="n"/>
       <c r="J29" s="8" t="n"/>
       <c r="K29" s="8" t="n"/>
-      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -1078,7 +1080,7 @@
       <c r="I30" s="8" t="n"/>
       <c r="J30" s="8" t="n"/>
       <c r="K30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -1098,7 +1100,7 @@
       <c r="I31" s="8" t="n"/>
       <c r="J31" s="8" t="n"/>
       <c r="K31" s="8" t="n"/>
-      <c r="L31" s="8" t="n"/>
+      <c r="M31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1118,7 +1120,7 @@
       <c r="I32" s="8" t="n"/>
       <c r="J32" s="8" t="n"/>
       <c r="K32" s="8" t="n"/>
-      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1138,7 +1140,7 @@
       <c r="I33" s="8" t="n"/>
       <c r="J33" s="8" t="n"/>
       <c r="K33" s="8" t="n"/>
-      <c r="L33" s="8" t="n"/>
+      <c r="M33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1158,7 +1160,7 @@
       <c r="I34" s="8" t="n"/>
       <c r="J34" s="8" t="n"/>
       <c r="K34" s="8" t="n"/>
-      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
@@ -1166,17 +1168,6 @@
           <t xml:space="preserve">  Precision</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="11" t="n"/>
-      <c r="J35" s="11" t="n"/>
-      <c r="K35" s="11" t="n"/>
-      <c r="L35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -1196,7 +1187,7 @@
       <c r="I36" s="13" t="n"/>
       <c r="J36" s="13" t="n"/>
       <c r="K36" s="13" t="n"/>
-      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="13" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -1216,7 +1207,7 @@
       <c r="I37" s="13" t="n"/>
       <c r="J37" s="13" t="n"/>
       <c r="K37" s="13" t="n"/>
-      <c r="L37" s="13" t="n"/>
+      <c r="M37" s="13" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -1236,7 +1227,7 @@
       <c r="I38" s="13" t="n"/>
       <c r="J38" s="13" t="n"/>
       <c r="K38" s="13" t="n"/>
-      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -1256,7 +1247,7 @@
       <c r="I39" s="13" t="n"/>
       <c r="J39" s="13" t="n"/>
       <c r="K39" s="13" t="n"/>
-      <c r="L39" s="13" t="n"/>
+      <c r="M39" s="13" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -1276,7 +1267,7 @@
       <c r="I40" s="13" t="n"/>
       <c r="J40" s="13" t="n"/>
       <c r="K40" s="13" t="n"/>
-      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="13" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -1296,7 +1287,7 @@
       <c r="I41" s="13" t="n"/>
       <c r="J41" s="13" t="n"/>
       <c r="K41" s="13" t="n"/>
-      <c r="L41" s="13" t="n"/>
+      <c r="M41" s="13" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -1316,7 +1307,7 @@
       <c r="I42" s="13" t="n"/>
       <c r="J42" s="13" t="n"/>
       <c r="K42" s="13" t="n"/>
-      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="13" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -1336,7 +1327,7 @@
       <c r="I43" s="13" t="n"/>
       <c r="J43" s="13" t="n"/>
       <c r="K43" s="13" t="n"/>
-      <c r="L43" s="13" t="n"/>
+      <c r="M43" s="13" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1356,7 +1347,7 @@
       <c r="I44" s="13" t="n"/>
       <c r="J44" s="13" t="n"/>
       <c r="K44" s="13" t="n"/>
-      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="13" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -1376,7 +1367,7 @@
       <c r="I45" s="13" t="n"/>
       <c r="J45" s="13" t="n"/>
       <c r="K45" s="13" t="n"/>
-      <c r="L45" s="13" t="n"/>
+      <c r="M45" s="13" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -1396,7 +1387,7 @@
       <c r="I46" s="13" t="n"/>
       <c r="J46" s="13" t="n"/>
       <c r="K46" s="13" t="n"/>
-      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="13" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -1416,7 +1407,7 @@
       <c r="I47" s="13" t="n"/>
       <c r="J47" s="13" t="n"/>
       <c r="K47" s="13" t="n"/>
-      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -1436,7 +1427,7 @@
       <c r="I48" s="13" t="n"/>
       <c r="J48" s="13" t="n"/>
       <c r="K48" s="13" t="n"/>
-      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="13" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -1456,7 +1447,7 @@
       <c r="I49" s="13" t="n"/>
       <c r="J49" s="13" t="n"/>
       <c r="K49" s="13" t="n"/>
-      <c r="L49" s="13" t="n"/>
+      <c r="M49" s="13" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -1476,7 +1467,7 @@
       <c r="I50" s="13" t="n"/>
       <c r="J50" s="13" t="n"/>
       <c r="K50" s="13" t="n"/>
-      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="13" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -1496,7 +1487,7 @@
       <c r="I51" s="13" t="n"/>
       <c r="J51" s="13" t="n"/>
       <c r="K51" s="13" t="n"/>
-      <c r="L51" s="13" t="n"/>
+      <c r="M51" s="13" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -1516,7 +1507,7 @@
       <c r="I52" s="13" t="n"/>
       <c r="J52" s="13" t="n"/>
       <c r="K52" s="13" t="n"/>
-      <c r="L52" s="13" t="n"/>
+      <c r="M52" s="13" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -1536,7 +1527,7 @@
       <c r="I53" s="13" t="n"/>
       <c r="J53" s="13" t="n"/>
       <c r="K53" s="13" t="n"/>
-      <c r="L53" s="13" t="n"/>
+      <c r="M53" s="13" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -1556,7 +1547,7 @@
       <c r="I54" s="13" t="n"/>
       <c r="J54" s="13" t="n"/>
       <c r="K54" s="13" t="n"/>
-      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="13" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -1576,7 +1567,7 @@
       <c r="I55" s="13" t="n"/>
       <c r="J55" s="13" t="n"/>
       <c r="K55" s="13" t="n"/>
-      <c r="L55" s="13" t="n"/>
+      <c r="M55" s="13" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
@@ -1584,17 +1575,6 @@
           <t xml:space="preserve">  Assembly</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n"/>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="16" t="n"/>
-      <c r="E56" s="17" t="n"/>
-      <c r="F56" s="16" t="n"/>
-      <c r="G56" s="16" t="n"/>
-      <c r="H56" s="16" t="n"/>
-      <c r="I56" s="16" t="n"/>
-      <c r="J56" s="16" t="n"/>
-      <c r="K56" s="16" t="n"/>
-      <c r="L56" s="16" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -1614,7 +1594,7 @@
       <c r="I57" s="18" t="n"/>
       <c r="J57" s="18" t="n"/>
       <c r="K57" s="18" t="n"/>
-      <c r="L57" s="18" t="n"/>
+      <c r="M57" s="18" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -1634,7 +1614,7 @@
       <c r="I58" s="18" t="n"/>
       <c r="J58" s="18" t="n"/>
       <c r="K58" s="18" t="n"/>
-      <c r="L58" s="18" t="n"/>
+      <c r="M58" s="18" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -1654,7 +1634,7 @@
       <c r="I59" s="18" t="n"/>
       <c r="J59" s="18" t="n"/>
       <c r="K59" s="18" t="n"/>
-      <c r="L59" s="18" t="n"/>
+      <c r="M59" s="18" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -1674,7 +1654,7 @@
       <c r="I60" s="18" t="n"/>
       <c r="J60" s="18" t="n"/>
       <c r="K60" s="18" t="n"/>
-      <c r="L60" s="18" t="n"/>
+      <c r="M60" s="18" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -1694,7 +1674,7 @@
       <c r="I61" s="18" t="n"/>
       <c r="J61" s="18" t="n"/>
       <c r="K61" s="18" t="n"/>
-      <c r="L61" s="18" t="n"/>
+      <c r="M61" s="18" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -1714,7 +1694,7 @@
       <c r="I62" s="18" t="n"/>
       <c r="J62" s="18" t="n"/>
       <c r="K62" s="18" t="n"/>
-      <c r="L62" s="18" t="n"/>
+      <c r="M62" s="18" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -1734,7 +1714,7 @@
       <c r="I63" s="18" t="n"/>
       <c r="J63" s="18" t="n"/>
       <c r="K63" s="18" t="n"/>
-      <c r="L63" s="18" t="n"/>
+      <c r="M63" s="18" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -1754,7 +1734,7 @@
       <c r="I64" s="18" t="n"/>
       <c r="J64" s="18" t="n"/>
       <c r="K64" s="18" t="n"/>
-      <c r="L64" s="18" t="n"/>
+      <c r="M64" s="18" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -1774,7 +1754,7 @@
       <c r="I65" s="18" t="n"/>
       <c r="J65" s="18" t="n"/>
       <c r="K65" s="18" t="n"/>
-      <c r="L65" s="18" t="n"/>
+      <c r="M65" s="18" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -1794,7 +1774,7 @@
       <c r="I66" s="18" t="n"/>
       <c r="J66" s="18" t="n"/>
       <c r="K66" s="18" t="n"/>
-      <c r="L66" s="18" t="n"/>
+      <c r="M66" s="18" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -1814,7 +1794,7 @@
       <c r="I67" s="18" t="n"/>
       <c r="J67" s="18" t="n"/>
       <c r="K67" s="18" t="n"/>
-      <c r="L67" s="18" t="n"/>
+      <c r="M67" s="18" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -1834,7 +1814,7 @@
       <c r="I68" s="18" t="n"/>
       <c r="J68" s="18" t="n"/>
       <c r="K68" s="18" t="n"/>
-      <c r="L68" s="18" t="n"/>
+      <c r="M68" s="18" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -1854,7 +1834,7 @@
       <c r="I69" s="18" t="n"/>
       <c r="J69" s="18" t="n"/>
       <c r="K69" s="18" t="n"/>
-      <c r="L69" s="18" t="n"/>
+      <c r="M69" s="18" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -1874,7 +1854,7 @@
       <c r="I70" s="18" t="n"/>
       <c r="J70" s="18" t="n"/>
       <c r="K70" s="18" t="n"/>
-      <c r="L70" s="18" t="n"/>
+      <c r="M70" s="18" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -1894,7 +1874,7 @@
       <c r="I71" s="18" t="n"/>
       <c r="J71" s="18" t="n"/>
       <c r="K71" s="18" t="n"/>
-      <c r="L71" s="18" t="n"/>
+      <c r="M71" s="18" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -1914,7 +1894,7 @@
       <c r="I72" s="18" t="n"/>
       <c r="J72" s="18" t="n"/>
       <c r="K72" s="18" t="n"/>
-      <c r="L72" s="18" t="n"/>
+      <c r="M72" s="18" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -1934,7 +1914,7 @@
       <c r="I73" s="18" t="n"/>
       <c r="J73" s="18" t="n"/>
       <c r="K73" s="18" t="n"/>
-      <c r="L73" s="18" t="n"/>
+      <c r="M73" s="18" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -1954,7 +1934,7 @@
       <c r="I74" s="18" t="n"/>
       <c r="J74" s="18" t="n"/>
       <c r="K74" s="18" t="n"/>
-      <c r="L74" s="18" t="n"/>
+      <c r="M74" s="18" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -1974,7 +1954,7 @@
       <c r="I75" s="18" t="n"/>
       <c r="J75" s="18" t="n"/>
       <c r="K75" s="18" t="n"/>
-      <c r="L75" s="18" t="n"/>
+      <c r="M75" s="18" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -1994,7 +1974,7 @@
       <c r="I76" s="18" t="n"/>
       <c r="J76" s="18" t="n"/>
       <c r="K76" s="18" t="n"/>
-      <c r="L76" s="18" t="n"/>
+      <c r="M76" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2008,15 +1988,12 @@
     <mergeCell ref="A35:L35"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="F9:F76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"success,fail,timeout,safety_stop"</formula1>
     </dataValidation>
     <dataValidation sqref="G9:G76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"grasp_geometry,kinematic_limit,perception,slip,force_limit,control_precision,other"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K9:K76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1,2,3"</formula1>
     </dataValidation>
     <dataValidation sqref="I9:I76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -2027,6 +2004,12 @@
     <dataValidation sqref="H9:H76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0.0</formula1>
     </dataValidation>
+    <dataValidation sqref="L9:L76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"prehensile,non_prehensile"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K9:K76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
